--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sanghyun/github/steel_iotable/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D9B1DD-4EF9-0D45-A43D-90390B00B298}"/>
   <bookViews>
-    <workbookView xWindow="25380" yWindow="2960" windowWidth="34400" windowHeight="18940" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
+    <workbookView xWindow="1900" yWindow="840" windowWidth="29400" windowHeight="17020" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
+    <sheet name="h2portion" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
   <si>
     <t>sector</t>
   </si>
@@ -61,12 +62,18 @@
   <si>
     <t>H2U</t>
   </si>
+  <si>
+    <t>total</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -80,6 +87,13 @@
       <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,10 +125,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,7 +470,7 @@
   <cols>
     <col min="1" max="1" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="28" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="28" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
@@ -550,83 +566,83 @@
       <c r="B2" s="2">
         <v>2711</v>
       </c>
-      <c r="C2">
-        <v>-100</v>
-      </c>
-      <c r="D2">
-        <v>-110</v>
-      </c>
-      <c r="E2">
-        <v>-120</v>
-      </c>
-      <c r="F2">
-        <v>-130</v>
-      </c>
-      <c r="G2">
-        <v>-140</v>
-      </c>
-      <c r="H2">
-        <v>-150</v>
-      </c>
-      <c r="I2">
-        <v>-160</v>
-      </c>
-      <c r="J2">
-        <v>-170</v>
-      </c>
-      <c r="K2">
-        <v>-180</v>
-      </c>
-      <c r="L2">
-        <v>-190</v>
-      </c>
-      <c r="M2">
-        <v>-200</v>
-      </c>
-      <c r="N2">
-        <v>-210</v>
-      </c>
-      <c r="O2">
-        <v>-220</v>
-      </c>
-      <c r="P2">
-        <v>-230</v>
-      </c>
-      <c r="Q2">
-        <v>-240</v>
-      </c>
-      <c r="R2">
-        <v>-250</v>
-      </c>
-      <c r="S2">
-        <v>-260</v>
-      </c>
-      <c r="T2">
-        <v>-270</v>
-      </c>
-      <c r="U2">
-        <v>-280</v>
-      </c>
-      <c r="V2">
-        <v>-290</v>
-      </c>
-      <c r="W2">
-        <v>-300</v>
-      </c>
-      <c r="X2">
-        <v>-310</v>
-      </c>
-      <c r="Y2">
-        <v>-320</v>
-      </c>
-      <c r="Z2">
-        <v>-330</v>
-      </c>
-      <c r="AA2">
-        <v>-340</v>
-      </c>
-      <c r="AB2">
-        <v>-350</v>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>-636028484.40622115</v>
+      </c>
+      <c r="E2" s="3">
+        <v>-1161255514.8874223</v>
+      </c>
+      <c r="F2" s="3">
+        <v>-1161255514.8874218</v>
+      </c>
+      <c r="G2" s="3">
+        <v>-1371346348.3328123</v>
+      </c>
+      <c r="H2" s="3">
+        <v>-3152149612.6058397</v>
+      </c>
+      <c r="I2" s="3">
+        <v>-3152149612.6058412</v>
+      </c>
+      <c r="J2" s="3">
+        <v>-3152149612.6058412</v>
+      </c>
+      <c r="K2" s="3">
+        <v>-4145573278.2804456</v>
+      </c>
+      <c r="L2" s="3">
+        <v>-4145573278.2804456</v>
+      </c>
+      <c r="M2" s="3">
+        <v>-5403129098.4650421</v>
+      </c>
+      <c r="N2" s="3">
+        <v>-6228563983.9188652</v>
+      </c>
+      <c r="O2" s="3">
+        <v>-6950163944.3933878</v>
+      </c>
+      <c r="P2" s="3">
+        <v>-6950163944.3933878</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>-6950163944.3933878</v>
+      </c>
+      <c r="R2" s="3">
+        <v>-7583661513.6934519</v>
+      </c>
+      <c r="S2" s="3">
+        <v>-7583661513.6934519</v>
+      </c>
+      <c r="T2" s="3">
+        <v>-8282886292.5491648</v>
+      </c>
+      <c r="U2" s="3">
+        <v>-8282886292.5491648</v>
+      </c>
+      <c r="V2" s="3">
+        <v>-8947849131.3262768</v>
+      </c>
+      <c r="W2" s="3">
+        <v>-8947849131.3262768</v>
+      </c>
+      <c r="X2" s="3">
+        <v>-9514046338.6238899</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>-9514046338.6238899</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>-9514046338.6238899</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>-9514046338.6238899</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>-9514046338.6238899</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -636,83 +652,83 @@
       <c r="B3" s="2">
         <v>4506</v>
       </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>55</v>
-      </c>
-      <c r="E3">
-        <v>60</v>
-      </c>
-      <c r="F3">
-        <v>65</v>
-      </c>
-      <c r="G3">
-        <v>70</v>
-      </c>
-      <c r="H3">
-        <v>75</v>
-      </c>
-      <c r="I3">
-        <v>80</v>
-      </c>
-      <c r="J3">
-        <v>85</v>
-      </c>
-      <c r="K3">
-        <v>90</v>
-      </c>
-      <c r="L3">
-        <v>95</v>
-      </c>
-      <c r="M3">
-        <v>100</v>
-      </c>
-      <c r="N3">
-        <v>105</v>
-      </c>
-      <c r="O3">
-        <v>110</v>
-      </c>
-      <c r="P3">
-        <v>115</v>
-      </c>
-      <c r="Q3">
-        <v>120</v>
-      </c>
-      <c r="R3">
-        <v>125</v>
-      </c>
-      <c r="S3">
-        <v>130</v>
-      </c>
-      <c r="T3">
-        <v>135</v>
-      </c>
-      <c r="U3">
-        <v>140</v>
-      </c>
-      <c r="V3">
-        <v>145</v>
-      </c>
-      <c r="W3">
-        <v>150</v>
-      </c>
-      <c r="X3">
-        <v>155</v>
-      </c>
-      <c r="Y3">
-        <v>160</v>
-      </c>
-      <c r="Z3">
-        <v>165</v>
-      </c>
-      <c r="AA3">
-        <v>170</v>
-      </c>
-      <c r="AB3">
-        <v>175</v>
+      <c r="C3" s="3">
+        <v>13545909750.548668</v>
+      </c>
+      <c r="D3" s="3">
+        <v>14819212824.570616</v>
+      </c>
+      <c r="E3" s="3">
+        <v>16172706688.913439</v>
+      </c>
+      <c r="F3" s="3">
+        <v>16819614956.469976</v>
+      </c>
+      <c r="G3" s="3">
+        <v>17821519770.741165</v>
+      </c>
+      <c r="H3" s="3">
+        <v>21820209720.085629</v>
+      </c>
+      <c r="I3" s="3">
+        <v>22693018108.889053</v>
+      </c>
+      <c r="J3" s="3">
+        <v>23911972695.901939</v>
+      </c>
+      <c r="K3" s="3">
+        <v>28357519930.870903</v>
+      </c>
+      <c r="L3" s="3">
+        <v>29491820728.105736</v>
+      </c>
+      <c r="M3" s="3">
+        <v>35530084303.933441</v>
+      </c>
+      <c r="N3" s="3">
+        <v>38653374832.799126</v>
+      </c>
+      <c r="O3" s="3">
+        <v>41429605318.09726</v>
+      </c>
+      <c r="P3" s="3">
+        <v>41429605318.09726</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>41429605318.09726</v>
+      </c>
+      <c r="R3" s="3">
+        <v>43859025623.070145</v>
+      </c>
+      <c r="S3" s="3">
+        <v>43859025623.070145</v>
+      </c>
+      <c r="T3" s="3">
+        <v>46565294400.521698</v>
+      </c>
+      <c r="U3" s="3">
+        <v>46565294400.521698</v>
+      </c>
+      <c r="V3" s="3">
+        <v>49063926823.614243</v>
+      </c>
+      <c r="W3" s="3">
+        <v>49063926823.614243</v>
+      </c>
+      <c r="X3" s="3">
+        <v>51215249339.896927</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>51215249339.896927</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>51215249339.896927</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>51215249339.896927</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>51215249339.896927</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -723,82 +739,82 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -809,82 +825,108 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>60</v>
+        <f>h2portion!C6*h2portion!C3</f>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>62</v>
+        <f>h2portion!D6*h2portion!D3</f>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>64</v>
+        <f>h2portion!E6*h2portion!E3</f>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>66</v>
+        <f>h2portion!F6*h2portion!F3</f>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>68</v>
+        <f>h2portion!G6*h2portion!G3</f>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>70</v>
+        <f>h2portion!H6*h2portion!H3</f>
+        <v>517553694.02880007</v>
       </c>
       <c r="I5">
-        <v>72</v>
+        <f>h2portion!I6*h2portion!I3</f>
+        <v>412167351.8329547</v>
       </c>
       <c r="J5">
-        <v>74</v>
+        <f>h2portion!J6*h2portion!J3</f>
+        <v>560146927.85662663</v>
       </c>
       <c r="K5">
-        <v>76</v>
+        <f>h2portion!K6*h2portion!K3</f>
+        <v>916125711.29999995</v>
       </c>
       <c r="L5">
-        <v>78</v>
+        <f>h2portion!L6*h2portion!L3</f>
+        <v>910610961.29999995</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <f>h2portion!M6*h2portion!M3</f>
+        <v>1365296642.0999999</v>
       </c>
       <c r="N5">
-        <v>82</v>
+        <f>h2portion!N6*h2portion!N3</f>
+        <v>1642420904.9999998</v>
       </c>
       <c r="O5">
-        <v>84</v>
+        <f>h2portion!O6*h2portion!O3</f>
+        <v>1784041250.1999998</v>
       </c>
       <c r="P5">
-        <v>86</v>
+        <f>h2portion!P6*h2portion!P3</f>
+        <v>1706935249.8</v>
       </c>
       <c r="Q5">
-        <v>88</v>
+        <f>h2portion!Q6*h2portion!Q3</f>
+        <v>1633362249.8</v>
       </c>
       <c r="R5">
-        <v>90</v>
+        <f>h2portion!R6*h2portion!R3</f>
+        <v>1751999073.4999998</v>
       </c>
       <c r="S5">
-        <v>92</v>
+        <f>h2portion!S6*h2portion!S3</f>
+        <v>1696500000</v>
       </c>
       <c r="T5">
-        <v>94</v>
+        <f>h2portion!T6*h2portion!T3</f>
+        <v>1819062805.5599999</v>
       </c>
       <c r="U5">
-        <v>96</v>
+        <f>h2portion!U6*h2portion!U3</f>
+        <v>1741739999.9999998</v>
       </c>
       <c r="V5">
-        <v>98</v>
+        <f>h2portion!V6*h2portion!V3</f>
+        <v>1832800115.9999998</v>
       </c>
       <c r="W5">
-        <v>100</v>
+        <f>h2portion!W6*h2portion!W3</f>
+        <v>1755370115.9999995</v>
       </c>
       <c r="X5">
-        <v>102</v>
+        <f>h2portion!X6*h2portion!X3</f>
+        <v>1811730174.9899995</v>
       </c>
       <c r="Y5">
-        <v>104</v>
+        <f>h2portion!Y6*h2portion!Y3</f>
+        <v>1735173674.9999998</v>
       </c>
       <c r="Z5">
-        <v>106</v>
+        <f>h2portion!Z6*h2portion!Z3</f>
+        <v>1662054525</v>
       </c>
       <c r="AA5">
-        <v>108</v>
+        <f>h2portion!AA6*h2portion!AA3</f>
+        <v>1592060000.01</v>
       </c>
       <c r="AB5">
-        <v>110</v>
+        <f>h2portion!AB6*h2portion!AB3</f>
+        <v>1525190475</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -895,82 +937,108 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <f>h2portion!C6*h2portion!C4</f>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <f>h2portion!D6*h2portion!D4</f>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <f>h2portion!E6*h2portion!E4</f>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <f>h2portion!F6*h2portion!F4</f>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>44</v>
+        <f>h2portion!G6*h2portion!G4</f>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>45</v>
+        <f>h2portion!H6*h2portion!H4</f>
+        <v>557365516.64640009</v>
       </c>
       <c r="I6">
-        <v>46</v>
+        <f>h2portion!I6*h2portion!I4</f>
+        <v>522398155.23014033</v>
       </c>
       <c r="J6">
-        <v>47</v>
+        <f>h2portion!J6*h2portion!J4</f>
+        <v>709953664.37642217</v>
       </c>
       <c r="K6">
-        <v>48</v>
+        <f>h2portion!K6*h2portion!K4</f>
+        <v>1161136075.95</v>
       </c>
       <c r="L6">
-        <v>49</v>
+        <f>h2portion!L6*h2portion!L4</f>
+        <v>1154146450.95</v>
       </c>
       <c r="M6">
-        <v>50</v>
+        <f>h2portion!M6*h2portion!M4</f>
+        <v>1730434116.1500001</v>
       </c>
       <c r="N6">
-        <v>51</v>
+        <f>h2portion!N6*h2portion!N4</f>
+        <v>2081673007.5</v>
       </c>
       <c r="O6">
-        <v>52</v>
+        <f>h2portion!O6*h2portion!O4</f>
+        <v>2261168561.3000002</v>
       </c>
       <c r="P6">
-        <v>53</v>
+        <f>h2portion!P6*h2portion!P4</f>
+        <v>2163441188.6999998</v>
       </c>
       <c r="Q6">
-        <v>54</v>
+        <f>h2portion!Q6*h2portion!Q4</f>
+        <v>2070191688.7</v>
       </c>
       <c r="R6">
-        <v>55</v>
+        <f>h2portion!R6*h2portion!R4</f>
+        <v>2220556965.25</v>
       </c>
       <c r="S6">
-        <v>56</v>
+        <f>h2portion!S6*h2portion!S4</f>
+        <v>1930500000</v>
       </c>
       <c r="T6">
-        <v>57</v>
+        <f>h2portion!T6*h2portion!T4</f>
+        <v>2069968020.1200001</v>
       </c>
       <c r="U6">
-        <v>58</v>
+        <f>h2portion!U6*h2portion!U4</f>
+        <v>1981980000</v>
       </c>
       <c r="V6">
-        <v>59</v>
+        <f>h2portion!V6*h2portion!V4</f>
+        <v>2085600132</v>
       </c>
       <c r="W6">
-        <v>60</v>
+        <f>h2portion!W6*h2portion!W4</f>
+        <v>1997490131.9999998</v>
       </c>
       <c r="X6">
-        <v>61</v>
+        <f>h2portion!X6*h2portion!X4</f>
+        <v>2061623992.2299998</v>
       </c>
       <c r="Y6">
-        <v>62</v>
+        <f>h2portion!Y6*h2portion!Y4</f>
+        <v>1974507975</v>
       </c>
       <c r="Z6">
-        <v>63</v>
+        <f>h2portion!Z6*h2portion!Z4</f>
+        <v>1891303425</v>
       </c>
       <c r="AA6">
-        <v>64</v>
+        <f>h2portion!AA6*h2portion!AA4</f>
+        <v>1811654482.77</v>
       </c>
       <c r="AB6">
-        <v>65</v>
+        <f>h2portion!AB6*h2portion!AB4</f>
+        <v>1735561575</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
@@ -981,82 +1049,634 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <f>h2portion!C6*h2portion!C5</f>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>54</v>
+        <f>h2portion!D6*h2portion!D5</f>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>58</v>
+        <f>h2portion!E6*h2portion!E5</f>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>62</v>
+        <f>h2portion!F6*h2portion!F5</f>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>66</v>
+        <f>h2portion!G6*h2portion!G5</f>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>70</v>
+        <f>h2portion!H6*h2portion!H5</f>
+        <v>2209556155.2768002</v>
       </c>
       <c r="I7">
-        <v>74</v>
+        <f>h2portion!I6*h2portion!I5</f>
+        <v>2199823424.3177471</v>
       </c>
       <c r="J7">
-        <v>78</v>
+        <f>h2portion!J6*h2portion!J5</f>
+        <v>2989621394.0254841</v>
       </c>
       <c r="K7">
-        <v>82</v>
+        <f>h2portion!K6*h2portion!K5</f>
+        <v>4889554668.4499998</v>
       </c>
       <c r="L7">
-        <v>86</v>
+        <f>h2portion!L6*h2portion!L5</f>
+        <v>4860121293.4499998</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <f>h2portion!M6*h2portion!M5</f>
+        <v>7286873938.6500006</v>
       </c>
       <c r="N7">
-        <v>94</v>
+        <f>h2portion!N6*h2portion!N5</f>
+        <v>8765944132.5</v>
       </c>
       <c r="O7">
-        <v>98</v>
+        <f>h2portion!O6*h2portion!O5</f>
+        <v>9521801556.3000011</v>
       </c>
       <c r="P7">
-        <v>102</v>
+        <f>h2portion!P6*h2portion!P5</f>
+        <v>9110270693.7000008</v>
       </c>
       <c r="Q7">
-        <v>106</v>
+        <f>h2portion!Q6*h2portion!Q5</f>
+        <v>8717596193.7000008</v>
       </c>
       <c r="R7">
-        <v>110</v>
+        <f>h2portion!R6*h2portion!R5</f>
+        <v>9350785752.75</v>
       </c>
       <c r="S7">
-        <v>114</v>
+        <f>h2portion!S6*h2portion!S5</f>
+        <v>8482500000</v>
       </c>
       <c r="T7">
-        <v>118</v>
+        <f>h2portion!T6*h2portion!T5</f>
+        <v>9095314027.7999992</v>
       </c>
       <c r="U7">
-        <v>122</v>
+        <f>h2portion!U6*h2portion!U5</f>
+        <v>8708700000</v>
       </c>
       <c r="V7">
-        <v>126</v>
+        <f>h2portion!V6*h2portion!V5</f>
+        <v>9164000580</v>
       </c>
       <c r="W7">
-        <v>130</v>
+        <f>h2portion!W6*h2portion!W5</f>
+        <v>8776850579.9999981</v>
       </c>
       <c r="X7">
-        <v>134</v>
+        <f>h2portion!X6*h2portion!X5</f>
+        <v>9058650874.9499989</v>
       </c>
       <c r="Y7">
-        <v>138</v>
+        <f>h2portion!Y6*h2portion!Y5</f>
+        <v>8675868375</v>
       </c>
       <c r="Z7">
-        <v>142</v>
+        <f>h2portion!Z6*h2portion!Z5</f>
+        <v>8310272625</v>
       </c>
       <c r="AA7">
-        <v>146</v>
+        <f>h2portion!AA6*h2portion!AA5</f>
+        <v>7960300000.0500002</v>
       </c>
       <c r="AB7">
-        <v>150</v>
+        <f>h2portion!AB6*h2portion!AB5</f>
+        <v>7625952375</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BACB8C9-B9B0-3742-97F6-4323486816FC}">
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="D2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="E2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="F2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="G2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="H2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="I2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="J2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="K2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="L2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="M2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="N2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="O2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="P2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="Q2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="R2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="S2">
+        <v>0.379</v>
+      </c>
+      <c r="T2">
+        <v>0.379</v>
+      </c>
+      <c r="U2">
+        <v>0.379</v>
+      </c>
+      <c r="V2">
+        <v>0.379</v>
+      </c>
+      <c r="W2">
+        <v>0.379</v>
+      </c>
+      <c r="X2">
+        <v>0.379</v>
+      </c>
+      <c r="Y2">
+        <v>0.379</v>
+      </c>
+      <c r="Z2">
+        <v>0.379</v>
+      </c>
+      <c r="AA2">
+        <v>0.379</v>
+      </c>
+      <c r="AB2">
+        <v>0.379</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0.104</v>
+      </c>
+      <c r="D3">
+        <v>0.104</v>
+      </c>
+      <c r="E3">
+        <v>0.104</v>
+      </c>
+      <c r="F3">
+        <v>0.104</v>
+      </c>
+      <c r="G3">
+        <v>0.104</v>
+      </c>
+      <c r="H3">
+        <v>0.104</v>
+      </c>
+      <c r="I3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="J3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="K3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="L3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="M3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="N3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="O3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="P3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="Q3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="R3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="S3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="T3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="U3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="V3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="W3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="X3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="Y3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="Z3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="AA3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="AB3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0.112</v>
+      </c>
+      <c r="D4">
+        <v>0.112</v>
+      </c>
+      <c r="E4">
+        <v>0.112</v>
+      </c>
+      <c r="F4">
+        <v>0.112</v>
+      </c>
+      <c r="G4">
+        <v>0.112</v>
+      </c>
+      <c r="H4">
+        <v>0.112</v>
+      </c>
+      <c r="I4">
+        <v>0.109</v>
+      </c>
+      <c r="J4">
+        <v>0.109</v>
+      </c>
+      <c r="K4">
+        <v>0.109</v>
+      </c>
+      <c r="L4">
+        <v>0.109</v>
+      </c>
+      <c r="M4">
+        <v>0.109</v>
+      </c>
+      <c r="N4">
+        <v>0.109</v>
+      </c>
+      <c r="O4">
+        <v>0.109</v>
+      </c>
+      <c r="P4">
+        <v>0.109</v>
+      </c>
+      <c r="Q4">
+        <v>0.109</v>
+      </c>
+      <c r="R4">
+        <v>0.109</v>
+      </c>
+      <c r="S4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="T4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="U4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="V4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="W4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="X4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="Y4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="Z4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="AA4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="AB4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="D5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="F5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="H5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="J5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="K5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="L5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="M5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="N5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="O5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="P5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="Q5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="R5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="S5">
+        <v>0.435</v>
+      </c>
+      <c r="T5">
+        <v>0.435</v>
+      </c>
+      <c r="U5">
+        <v>0.435</v>
+      </c>
+      <c r="V5">
+        <v>0.435</v>
+      </c>
+      <c r="W5">
+        <v>0.435</v>
+      </c>
+      <c r="X5">
+        <v>0.435</v>
+      </c>
+      <c r="Y5">
+        <v>0.435</v>
+      </c>
+      <c r="Z5">
+        <v>0.435</v>
+      </c>
+      <c r="AA5">
+        <v>0.435</v>
+      </c>
+      <c r="AB5">
+        <v>0.435</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>4976477827.2000008</v>
+      </c>
+      <c r="I6">
+        <v>4792643625.9645901</v>
+      </c>
+      <c r="J6">
+        <v>6513336370.4258909</v>
+      </c>
+      <c r="K6">
+        <v>10652624550</v>
+      </c>
+      <c r="L6">
+        <v>10588499550</v>
+      </c>
+      <c r="M6">
+        <v>15875542350</v>
+      </c>
+      <c r="N6">
+        <v>19097917500</v>
+      </c>
+      <c r="O6">
+        <v>20744665700</v>
+      </c>
+      <c r="P6">
+        <v>19848084300</v>
+      </c>
+      <c r="Q6">
+        <v>18992584300</v>
+      </c>
+      <c r="R6">
+        <v>20372082250</v>
+      </c>
+      <c r="S6">
+        <v>19500000000</v>
+      </c>
+      <c r="T6">
+        <v>20908767880</v>
+      </c>
+      <c r="U6">
+        <v>20020000000</v>
+      </c>
+      <c r="V6">
+        <v>21066668000</v>
+      </c>
+      <c r="W6">
+        <v>20176667999.999996</v>
+      </c>
+      <c r="X6">
+        <v>20824484769.999996</v>
+      </c>
+      <c r="Y6">
+        <v>19944525000</v>
+      </c>
+      <c r="Z6">
+        <v>19104075000</v>
+      </c>
+      <c r="AA6">
+        <v>18299540230</v>
+      </c>
+      <c r="AB6">
+        <v>17530925000</v>
       </c>
     </row>
   </sheetData>

--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D9B1DD-4EF9-0D45-A43D-90390B00B298}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A6F563-1CBE-564A-97B8-3D9CC85EB1D4}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="840" windowWidth="29400" windowHeight="17020" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="29400" windowHeight="17020" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="10">
   <si>
     <t>sector</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>total</t>
+  </si>
+  <si>
+    <t>4506</t>
   </si>
 </sst>
 </file>
@@ -128,9 +131,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -146,6 +149,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -563,85 +570,85 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>2711</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
         <v>-636028484.40622115</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>-1161255514.8874223</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>-1161255514.8874218</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>-1371346348.3328123</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>-3152149612.6058397</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>-3152149612.6058412</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>-3152149612.6058412</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="2">
         <v>-4145573278.2804456</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>-4145573278.2804456</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <v>-5403129098.4650421</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="2">
         <v>-6228563983.9188652</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>-6950163944.3933878</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>-6950163944.3933878</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="2">
         <v>-6950163944.3933878</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="2">
         <v>-7583661513.6934519</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="2">
         <v>-7583661513.6934519</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="2">
         <v>-8282886292.5491648</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2" s="2">
         <v>-8282886292.5491648</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2" s="2">
         <v>-8947849131.3262768</v>
       </c>
-      <c r="W2" s="3">
+      <c r="W2" s="2">
         <v>-8947849131.3262768</v>
       </c>
-      <c r="X2" s="3">
+      <c r="X2" s="2">
         <v>-9514046338.6238899</v>
       </c>
-      <c r="Y2" s="3">
+      <c r="Y2" s="2">
         <v>-9514046338.6238899</v>
       </c>
-      <c r="Z2" s="3">
+      <c r="Z2" s="2">
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AA2" s="3">
+      <c r="AA2" s="2">
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AB2" s="3">
+      <c r="AB2" s="2">
         <v>-9514046338.6238899</v>
       </c>
     </row>
@@ -649,85 +656,85 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>4506</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
         <v>13545909750.548668</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>14819212824.570616</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>16172706688.913439</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>16819614956.469976</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>17821519770.741165</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>21820209720.085629</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>22693018108.889053</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>23911972695.901939</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <v>28357519930.870903</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>29491820728.105736</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <v>35530084303.933441</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>38653374832.799126</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="2">
         <v>41429605318.09726</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <v>41429605318.09726</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <v>41429605318.09726</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <v>43859025623.070145</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <v>43859025623.070145</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <v>46565294400.521698</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="2">
         <v>46565294400.521698</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3" s="2">
         <v>49063926823.614243</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="2">
         <v>49063926823.614243</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="2">
         <v>51215249339.896927</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y3" s="2">
         <v>51215249339.896927</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="Z3" s="2">
         <v>51215249339.896927</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AA3" s="2">
         <v>51215249339.896927</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AB3" s="2">
         <v>51215249339.896927</v>
       </c>
     </row>
@@ -1597,7 +1604,7 @@
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C6">

--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A6F563-1CBE-564A-97B8-3D9CC85EB1D4}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B365F1D-BCEE-614F-A11E-F3074436038B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="840" windowWidth="29400" windowHeight="17020" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="11">
   <si>
     <t>sector</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>4506</t>
+  </si>
+  <si>
+    <t>2711</t>
   </si>
 </sst>
 </file>
@@ -570,8 +573,8 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
-        <v>2711</v>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>

--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B365F1D-BCEE-614F-A11E-F3074436038B}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4362B0D-4C52-9745-8577-0EDBBA09B077}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="840" windowWidth="29400" windowHeight="17020" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16940" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
     <t>4506</t>
   </si>
   <si>
-    <t>2711</t>
+    <t>1610</t>
   </si>
 </sst>
 </file>

--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4362B0D-4C52-9745-8577-0EDBBA09B077}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8A8E98D-005E-8147-9A21-C5FA3D5947D2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16940" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
+    <workbookView xWindow="-4720" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -131,12 +131,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2733D29-791A-6C4C-8C8F-CBDD0CD69075}">
-  <dimension ref="A1:AB7"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" bestFit="1" customWidth="1"/>
@@ -580,79 +581,79 @@
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>-636028484.40622115</v>
+        <v>-636028.48440622119</v>
       </c>
       <c r="E2" s="2">
-        <v>-1161255514.8874223</v>
+        <v>-1161255.5148874223</v>
       </c>
       <c r="F2" s="2">
-        <v>-1161255514.8874218</v>
+        <v>-1161255.5148874219</v>
       </c>
       <c r="G2" s="2">
-        <v>-1371346348.3328123</v>
+        <v>-1371346.3483328123</v>
       </c>
       <c r="H2" s="2">
-        <v>-3152149612.6058397</v>
+        <v>-3152149.6126058395</v>
       </c>
       <c r="I2" s="2">
-        <v>-3152149612.6058412</v>
+        <v>-3152149.6126058414</v>
       </c>
       <c r="J2" s="2">
-        <v>-3152149612.6058412</v>
+        <v>-3152149.6126058414</v>
       </c>
       <c r="K2" s="2">
-        <v>-4145573278.2804456</v>
+        <v>-4145573.2782804454</v>
       </c>
       <c r="L2" s="2">
-        <v>-4145573278.2804456</v>
+        <v>-4145573.2782804454</v>
       </c>
       <c r="M2" s="2">
-        <v>-5403129098.4650421</v>
+        <v>-5403129.0984650422</v>
       </c>
       <c r="N2" s="2">
-        <v>-6228563983.9188652</v>
+        <v>-6228563.9839188652</v>
       </c>
       <c r="O2" s="2">
-        <v>-6950163944.3933878</v>
+        <v>-6950163.944393388</v>
       </c>
       <c r="P2" s="2">
-        <v>-6950163944.3933878</v>
+        <v>-6950163.944393388</v>
       </c>
       <c r="Q2" s="2">
-        <v>-6950163944.3933878</v>
+        <v>-6950163.944393388</v>
       </c>
       <c r="R2" s="2">
-        <v>-7583661513.6934519</v>
+        <v>-7583661.5136934519</v>
       </c>
       <c r="S2" s="2">
-        <v>-7583661513.6934519</v>
+        <v>-7583661.5136934519</v>
       </c>
       <c r="T2" s="2">
-        <v>-8282886292.5491648</v>
+        <v>-8282886.292549165</v>
       </c>
       <c r="U2" s="2">
-        <v>-8282886292.5491648</v>
+        <v>-8282886.292549165</v>
       </c>
       <c r="V2" s="2">
-        <v>-8947849131.3262768</v>
+        <v>-8947849.1313262768</v>
       </c>
       <c r="W2" s="2">
-        <v>-8947849131.3262768</v>
+        <v>-8947849.1313262768</v>
       </c>
       <c r="X2" s="2">
-        <v>-9514046338.6238899</v>
+        <v>-9514046.3386238907</v>
       </c>
       <c r="Y2" s="2">
-        <v>-9514046338.6238899</v>
+        <v>-9514046.3386238907</v>
       </c>
       <c r="Z2" s="2">
-        <v>-9514046338.6238899</v>
+        <v>-9514046.3386238907</v>
       </c>
       <c r="AA2" s="2">
-        <v>-9514046338.6238899</v>
+        <v>-9514046.3386238907</v>
       </c>
       <c r="AB2" s="2">
-        <v>-9514046338.6238899</v>
+        <v>-9514046.3386238907</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -663,82 +664,82 @@
         <v>9</v>
       </c>
       <c r="C3" s="2">
-        <v>13545909750.548668</v>
+        <v>13545909.750548668</v>
       </c>
       <c r="D3" s="2">
-        <v>14819212824.570616</v>
+        <v>14819212.824570615</v>
       </c>
       <c r="E3" s="2">
-        <v>16172706688.913439</v>
+        <v>16172706.688913438</v>
       </c>
       <c r="F3" s="2">
-        <v>16819614956.469976</v>
+        <v>16819614.956469975</v>
       </c>
       <c r="G3" s="2">
-        <v>17821519770.741165</v>
+        <v>17821519.770741165</v>
       </c>
       <c r="H3" s="2">
-        <v>21820209720.085629</v>
+        <v>21820209.720085628</v>
       </c>
       <c r="I3" s="2">
-        <v>22693018108.889053</v>
+        <v>22693018.108889055</v>
       </c>
       <c r="J3" s="2">
-        <v>23911972695.901939</v>
+        <v>23911972.695901938</v>
       </c>
       <c r="K3" s="2">
-        <v>28357519930.870903</v>
+        <v>28357519.930870902</v>
       </c>
       <c r="L3" s="2">
-        <v>29491820728.105736</v>
+        <v>29491820.728105735</v>
       </c>
       <c r="M3" s="2">
-        <v>35530084303.933441</v>
+        <v>35530084.303933442</v>
       </c>
       <c r="N3" s="2">
-        <v>38653374832.799126</v>
+        <v>38653374.832799129</v>
       </c>
       <c r="O3" s="2">
-        <v>41429605318.09726</v>
+        <v>41429605.318097256</v>
       </c>
       <c r="P3" s="2">
-        <v>41429605318.09726</v>
+        <v>41429605.318097256</v>
       </c>
       <c r="Q3" s="2">
-        <v>41429605318.09726</v>
+        <v>41429605.318097256</v>
       </c>
       <c r="R3" s="2">
-        <v>43859025623.070145</v>
+        <v>43859025.623070143</v>
       </c>
       <c r="S3" s="2">
-        <v>43859025623.070145</v>
+        <v>43859025.623070143</v>
       </c>
       <c r="T3" s="2">
-        <v>46565294400.521698</v>
+        <v>46565294.400521696</v>
       </c>
       <c r="U3" s="2">
-        <v>46565294400.521698</v>
+        <v>46565294.400521696</v>
       </c>
       <c r="V3" s="2">
-        <v>49063926823.614243</v>
+        <v>49063926.82361424</v>
       </c>
       <c r="W3" s="2">
-        <v>49063926823.614243</v>
+        <v>49063926.82361424</v>
       </c>
       <c r="X3" s="2">
-        <v>51215249339.896927</v>
+        <v>51215249.339896925</v>
       </c>
       <c r="Y3" s="2">
-        <v>51215249339.896927</v>
+        <v>51215249.339896925</v>
       </c>
       <c r="Z3" s="2">
-        <v>51215249339.896927</v>
+        <v>51215249.339896925</v>
       </c>
       <c r="AA3" s="2">
-        <v>51215249339.896927</v>
+        <v>51215249.339896925</v>
       </c>
       <c r="AB3" s="2">
-        <v>51215249339.896927</v>
+        <v>51215249.339896925</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -835,108 +836,82 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <f>h2portion!C6*h2portion!C3</f>
         <v>0</v>
       </c>
       <c r="D5">
-        <f>h2portion!D6*h2portion!D3</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>h2portion!E6*h2portion!E3</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>h2portion!F6*h2portion!F3</f>
         <v>0</v>
       </c>
       <c r="G5">
-        <f>h2portion!G6*h2portion!G3</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <f>h2portion!H6*h2portion!H3</f>
-        <v>517553694.02880007</v>
+        <v>517553.69402880006</v>
       </c>
       <c r="I5">
-        <f>h2portion!I6*h2portion!I3</f>
-        <v>412167351.8329547</v>
+        <v>412167.35183295468</v>
       </c>
       <c r="J5">
-        <f>h2portion!J6*h2portion!J3</f>
-        <v>560146927.85662663</v>
+        <v>560146.92785662669</v>
       </c>
       <c r="K5">
-        <f>h2portion!K6*h2portion!K3</f>
-        <v>916125711.29999995</v>
+        <v>916125.71129999997</v>
       </c>
       <c r="L5">
-        <f>h2portion!L6*h2portion!L3</f>
-        <v>910610961.29999995</v>
+        <v>910610.96129999997</v>
       </c>
       <c r="M5">
-        <f>h2portion!M6*h2portion!M3</f>
-        <v>1365296642.0999999</v>
+        <v>1365296.6420999998</v>
       </c>
       <c r="N5">
-        <f>h2portion!N6*h2portion!N3</f>
-        <v>1642420904.9999998</v>
+        <v>1642420.9049999998</v>
       </c>
       <c r="O5">
-        <f>h2portion!O6*h2portion!O3</f>
-        <v>1784041250.1999998</v>
+        <v>1784041.2501999999</v>
       </c>
       <c r="P5">
-        <f>h2portion!P6*h2portion!P3</f>
-        <v>1706935249.8</v>
+        <v>1706935.2497999999</v>
       </c>
       <c r="Q5">
-        <f>h2portion!Q6*h2portion!Q3</f>
-        <v>1633362249.8</v>
+        <v>1633362.2497999999</v>
       </c>
       <c r="R5">
-        <f>h2portion!R6*h2portion!R3</f>
-        <v>1751999073.4999998</v>
+        <v>1751999.0734999997</v>
       </c>
       <c r="S5">
-        <f>h2portion!S6*h2portion!S3</f>
-        <v>1696500000</v>
+        <v>1696500</v>
       </c>
       <c r="T5">
-        <f>h2portion!T6*h2portion!T3</f>
-        <v>1819062805.5599999</v>
+        <v>1819062.80556</v>
       </c>
       <c r="U5">
-        <f>h2portion!U6*h2portion!U3</f>
-        <v>1741739999.9999998</v>
+        <v>1741739.9999999998</v>
       </c>
       <c r="V5">
-        <f>h2portion!V6*h2portion!V3</f>
-        <v>1832800115.9999998</v>
+        <v>1832800.1159999997</v>
       </c>
       <c r="W5">
-        <f>h2portion!W6*h2portion!W3</f>
-        <v>1755370115.9999995</v>
+        <v>1755370.1159999995</v>
       </c>
       <c r="X5">
-        <f>h2portion!X6*h2portion!X3</f>
-        <v>1811730174.9899995</v>
+        <v>1811730.1749899995</v>
       </c>
       <c r="Y5">
-        <f>h2portion!Y6*h2portion!Y3</f>
-        <v>1735173674.9999998</v>
+        <v>1735173.6749999998</v>
       </c>
       <c r="Z5">
-        <f>h2portion!Z6*h2portion!Z3</f>
-        <v>1662054525</v>
+        <v>1662054.5249999999</v>
       </c>
       <c r="AA5">
-        <f>h2portion!AA6*h2portion!AA3</f>
-        <v>1592060000.01</v>
+        <v>1592060.0000100001</v>
       </c>
       <c r="AB5">
-        <f>h2portion!AB6*h2portion!AB3</f>
-        <v>1525190475</v>
+        <v>1525190.4750000001</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -947,108 +922,82 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <f>h2portion!C6*h2portion!C4</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>h2portion!D6*h2portion!D4</f>
         <v>0</v>
       </c>
       <c r="E6">
-        <f>h2portion!E6*h2portion!E4</f>
         <v>0</v>
       </c>
       <c r="F6">
-        <f>h2portion!F6*h2portion!F4</f>
         <v>0</v>
       </c>
       <c r="G6">
-        <f>h2portion!G6*h2portion!G4</f>
         <v>0</v>
       </c>
       <c r="H6">
-        <f>h2portion!H6*h2portion!H4</f>
-        <v>557365516.64640009</v>
+        <v>557365.51664640009</v>
       </c>
       <c r="I6">
-        <f>h2portion!I6*h2portion!I4</f>
-        <v>522398155.23014033</v>
+        <v>522398.15523014031</v>
       </c>
       <c r="J6">
-        <f>h2portion!J6*h2portion!J4</f>
-        <v>709953664.37642217</v>
+        <v>709953.66437642218</v>
       </c>
       <c r="K6">
-        <f>h2portion!K6*h2portion!K4</f>
-        <v>1161136075.95</v>
+        <v>1161136.07595</v>
       </c>
       <c r="L6">
-        <f>h2portion!L6*h2portion!L4</f>
-        <v>1154146450.95</v>
+        <v>1154146.45095</v>
       </c>
       <c r="M6">
-        <f>h2portion!M6*h2portion!M4</f>
-        <v>1730434116.1500001</v>
+        <v>1730434.1161500001</v>
       </c>
       <c r="N6">
-        <f>h2portion!N6*h2portion!N4</f>
-        <v>2081673007.5</v>
+        <v>2081673.0075000001</v>
       </c>
       <c r="O6">
-        <f>h2portion!O6*h2portion!O4</f>
-        <v>2261168561.3000002</v>
+        <v>2261168.5613000002</v>
       </c>
       <c r="P6">
-        <f>h2portion!P6*h2portion!P4</f>
-        <v>2163441188.6999998</v>
+        <v>2163441.1886999998</v>
       </c>
       <c r="Q6">
-        <f>h2portion!Q6*h2portion!Q4</f>
-        <v>2070191688.7</v>
+        <v>2070191.6887000001</v>
       </c>
       <c r="R6">
-        <f>h2portion!R6*h2portion!R4</f>
-        <v>2220556965.25</v>
+        <v>2220556.9652499999</v>
       </c>
       <c r="S6">
-        <f>h2portion!S6*h2portion!S4</f>
-        <v>1930500000</v>
+        <v>1930500</v>
       </c>
       <c r="T6">
-        <f>h2portion!T6*h2portion!T4</f>
-        <v>2069968020.1200001</v>
+        <v>2069968.0201200002</v>
       </c>
       <c r="U6">
-        <f>h2portion!U6*h2portion!U4</f>
-        <v>1981980000</v>
+        <v>1981980</v>
       </c>
       <c r="V6">
-        <f>h2portion!V6*h2portion!V4</f>
-        <v>2085600132</v>
+        <v>2085600.132</v>
       </c>
       <c r="W6">
-        <f>h2portion!W6*h2portion!W4</f>
-        <v>1997490131.9999998</v>
+        <v>1997490.1319999998</v>
       </c>
       <c r="X6">
-        <f>h2portion!X6*h2portion!X4</f>
-        <v>2061623992.2299998</v>
+        <v>2061623.9922299997</v>
       </c>
       <c r="Y6">
-        <f>h2portion!Y6*h2portion!Y4</f>
-        <v>1974507975</v>
+        <v>1974507.9750000001</v>
       </c>
       <c r="Z6">
-        <f>h2portion!Z6*h2portion!Z4</f>
-        <v>1891303425</v>
+        <v>1891303.425</v>
       </c>
       <c r="AA6">
-        <f>h2portion!AA6*h2portion!AA4</f>
-        <v>1811654482.77</v>
+        <v>1811654.4827699999</v>
       </c>
       <c r="AB6">
-        <f>h2portion!AB6*h2portion!AB4</f>
-        <v>1735561575</v>
+        <v>1735561.575</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
@@ -1059,109 +1008,251 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <f>h2portion!C6*h2portion!C5</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>h2portion!D6*h2portion!D5</f>
         <v>0</v>
       </c>
       <c r="E7">
-        <f>h2portion!E6*h2portion!E5</f>
         <v>0</v>
       </c>
       <c r="F7">
-        <f>h2portion!F6*h2portion!F5</f>
         <v>0</v>
       </c>
       <c r="G7">
-        <f>h2portion!G6*h2portion!G5</f>
         <v>0</v>
       </c>
       <c r="H7">
-        <f>h2portion!H6*h2portion!H5</f>
-        <v>2209556155.2768002</v>
+        <v>2209556.1552768</v>
       </c>
       <c r="I7">
-        <f>h2portion!I6*h2portion!I5</f>
-        <v>2199823424.3177471</v>
+        <v>2199823.4243177469</v>
       </c>
       <c r="J7">
-        <f>h2portion!J6*h2portion!J5</f>
-        <v>2989621394.0254841</v>
+        <v>2989621.3940254841</v>
       </c>
       <c r="K7">
-        <f>h2portion!K6*h2portion!K5</f>
-        <v>4889554668.4499998</v>
+        <v>4889554.6684499998</v>
       </c>
       <c r="L7">
-        <f>h2portion!L6*h2portion!L5</f>
-        <v>4860121293.4499998</v>
+        <v>4860121.2934499998</v>
       </c>
       <c r="M7">
-        <f>h2portion!M6*h2portion!M5</f>
-        <v>7286873938.6500006</v>
+        <v>7286873.9386500008</v>
       </c>
       <c r="N7">
-        <f>h2portion!N6*h2portion!N5</f>
-        <v>8765944132.5</v>
+        <v>8765944.1325000003</v>
       </c>
       <c r="O7">
-        <f>h2portion!O6*h2portion!O5</f>
-        <v>9521801556.3000011</v>
+        <v>9521801.5563000012</v>
       </c>
       <c r="P7">
-        <f>h2portion!P6*h2portion!P5</f>
-        <v>9110270693.7000008</v>
+        <v>9110270.6937000006</v>
       </c>
       <c r="Q7">
-        <f>h2portion!Q6*h2portion!Q5</f>
-        <v>8717596193.7000008</v>
+        <v>8717596.1937000006</v>
       </c>
       <c r="R7">
-        <f>h2portion!R6*h2portion!R5</f>
-        <v>9350785752.75</v>
+        <v>9350785.75275</v>
       </c>
       <c r="S7">
-        <f>h2portion!S6*h2portion!S5</f>
-        <v>8482500000</v>
+        <v>8482500</v>
       </c>
       <c r="T7">
-        <f>h2portion!T6*h2portion!T5</f>
-        <v>9095314027.7999992</v>
+        <v>9095314.0277999993</v>
       </c>
       <c r="U7">
-        <f>h2portion!U6*h2portion!U5</f>
-        <v>8708700000</v>
+        <v>8708700</v>
       </c>
       <c r="V7">
-        <f>h2portion!V6*h2portion!V5</f>
-        <v>9164000580</v>
+        <v>9164000.5800000001</v>
       </c>
       <c r="W7">
-        <f>h2portion!W6*h2portion!W5</f>
-        <v>8776850579.9999981</v>
+        <v>8776850.5799999982</v>
       </c>
       <c r="X7">
-        <f>h2portion!X6*h2portion!X5</f>
-        <v>9058650874.9499989</v>
+        <v>9058650.8749499992</v>
       </c>
       <c r="Y7">
-        <f>h2portion!Y6*h2portion!Y5</f>
-        <v>8675868375</v>
+        <v>8675868.375</v>
       </c>
       <c r="Z7">
-        <f>h2portion!Z6*h2portion!Z5</f>
-        <v>8310272625</v>
+        <v>8310272.625</v>
       </c>
       <c r="AA7">
-        <f>h2portion!AA6*h2portion!AA5</f>
-        <v>7960300000.0500002</v>
+        <v>7960300.0000499999</v>
       </c>
       <c r="AB7">
-        <f>h2portion!AB6*h2portion!AB5</f>
-        <v>7625952375</v>
-      </c>
+        <v>7625952.375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8A8E98D-005E-8147-9A21-C5FA3D5947D2}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90EDCEDF-9F7E-694E-8ED3-E824D6A77DDF}"/>
   <bookViews>
-    <workbookView xWindow="-4720" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
+    <workbookView xWindow="-9700" yWindow="760" windowWidth="25720" windowHeight="16980" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>517553.69402880006</v>
+        <v>517553.6940288</v>
       </c>
       <c r="I5">
         <v>412167.35183295468</v>
@@ -1263,6 +1263,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BACB8C9-B9B0-3742-97F6-4323486816FC}">
   <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1717,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4976477827.2000008</v>
+        <v>4976477827.1999998</v>
       </c>
       <c r="I6">
         <v>4792643625.9645901</v>

--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sanghyun/github/steel_iotable/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8A8E98D-005E-8147-9A21-C5FA3D5947D2}"/>
   <bookViews>
-    <workbookView xWindow="25380" yWindow="2960" windowWidth="34400" windowHeight="18940" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
+    <workbookView xWindow="-4720" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
+    <sheet name="h2portion" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="11">
   <si>
     <t>sector</t>
   </si>
@@ -61,12 +62,24 @@
   <si>
     <t>H2U</t>
   </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>4506</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -80,6 +93,13 @@
       <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,10 +131,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -130,6 +153,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,12 +476,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2733D29-791A-6C4C-8C8F-CBDD0CD69075}">
-  <dimension ref="A1:AB7"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="28" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="28" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
@@ -547,172 +574,172 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
-        <v>2711</v>
-      </c>
-      <c r="C2">
-        <v>-100</v>
-      </c>
-      <c r="D2">
-        <v>-110</v>
-      </c>
-      <c r="E2">
-        <v>-120</v>
-      </c>
-      <c r="F2">
-        <v>-130</v>
-      </c>
-      <c r="G2">
-        <v>-140</v>
-      </c>
-      <c r="H2">
-        <v>-150</v>
-      </c>
-      <c r="I2">
-        <v>-160</v>
-      </c>
-      <c r="J2">
-        <v>-170</v>
-      </c>
-      <c r="K2">
-        <v>-180</v>
-      </c>
-      <c r="L2">
-        <v>-190</v>
-      </c>
-      <c r="M2">
-        <v>-200</v>
-      </c>
-      <c r="N2">
-        <v>-210</v>
-      </c>
-      <c r="O2">
-        <v>-220</v>
-      </c>
-      <c r="P2">
-        <v>-230</v>
-      </c>
-      <c r="Q2">
-        <v>-240</v>
-      </c>
-      <c r="R2">
-        <v>-250</v>
-      </c>
-      <c r="S2">
-        <v>-260</v>
-      </c>
-      <c r="T2">
-        <v>-270</v>
-      </c>
-      <c r="U2">
-        <v>-280</v>
-      </c>
-      <c r="V2">
-        <v>-290</v>
-      </c>
-      <c r="W2">
-        <v>-300</v>
-      </c>
-      <c r="X2">
-        <v>-310</v>
-      </c>
-      <c r="Y2">
-        <v>-320</v>
-      </c>
-      <c r="Z2">
-        <v>-330</v>
-      </c>
-      <c r="AA2">
-        <v>-340</v>
-      </c>
-      <c r="AB2">
-        <v>-350</v>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>-636028.48440622119</v>
+      </c>
+      <c r="E2" s="2">
+        <v>-1161255.5148874223</v>
+      </c>
+      <c r="F2" s="2">
+        <v>-1161255.5148874219</v>
+      </c>
+      <c r="G2" s="2">
+        <v>-1371346.3483328123</v>
+      </c>
+      <c r="H2" s="2">
+        <v>-3152149.6126058395</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-3152149.6126058414</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-3152149.6126058414</v>
+      </c>
+      <c r="K2" s="2">
+        <v>-4145573.2782804454</v>
+      </c>
+      <c r="L2" s="2">
+        <v>-4145573.2782804454</v>
+      </c>
+      <c r="M2" s="2">
+        <v>-5403129.0984650422</v>
+      </c>
+      <c r="N2" s="2">
+        <v>-6228563.9839188652</v>
+      </c>
+      <c r="O2" s="2">
+        <v>-6950163.944393388</v>
+      </c>
+      <c r="P2" s="2">
+        <v>-6950163.944393388</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>-6950163.944393388</v>
+      </c>
+      <c r="R2" s="2">
+        <v>-7583661.5136934519</v>
+      </c>
+      <c r="S2" s="2">
+        <v>-7583661.5136934519</v>
+      </c>
+      <c r="T2" s="2">
+        <v>-8282886.292549165</v>
+      </c>
+      <c r="U2" s="2">
+        <v>-8282886.292549165</v>
+      </c>
+      <c r="V2" s="2">
+        <v>-8947849.1313262768</v>
+      </c>
+      <c r="W2" s="2">
+        <v>-8947849.1313262768</v>
+      </c>
+      <c r="X2" s="2">
+        <v>-9514046.3386238907</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>-9514046.3386238907</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>-9514046.3386238907</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>-9514046.3386238907</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>-9514046.3386238907</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>4506</v>
-      </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>55</v>
-      </c>
-      <c r="E3">
-        <v>60</v>
-      </c>
-      <c r="F3">
-        <v>65</v>
-      </c>
-      <c r="G3">
-        <v>70</v>
-      </c>
-      <c r="H3">
-        <v>75</v>
-      </c>
-      <c r="I3">
-        <v>80</v>
-      </c>
-      <c r="J3">
-        <v>85</v>
-      </c>
-      <c r="K3">
-        <v>90</v>
-      </c>
-      <c r="L3">
-        <v>95</v>
-      </c>
-      <c r="M3">
-        <v>100</v>
-      </c>
-      <c r="N3">
-        <v>105</v>
-      </c>
-      <c r="O3">
-        <v>110</v>
-      </c>
-      <c r="P3">
-        <v>115</v>
-      </c>
-      <c r="Q3">
-        <v>120</v>
-      </c>
-      <c r="R3">
-        <v>125</v>
-      </c>
-      <c r="S3">
-        <v>130</v>
-      </c>
-      <c r="T3">
-        <v>135</v>
-      </c>
-      <c r="U3">
-        <v>140</v>
-      </c>
-      <c r="V3">
-        <v>145</v>
-      </c>
-      <c r="W3">
-        <v>150</v>
-      </c>
-      <c r="X3">
-        <v>155</v>
-      </c>
-      <c r="Y3">
-        <v>160</v>
-      </c>
-      <c r="Z3">
-        <v>165</v>
-      </c>
-      <c r="AA3">
-        <v>170</v>
-      </c>
-      <c r="AB3">
-        <v>175</v>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>13545909.750548668</v>
+      </c>
+      <c r="D3" s="2">
+        <v>14819212.824570615</v>
+      </c>
+      <c r="E3" s="2">
+        <v>16172706.688913438</v>
+      </c>
+      <c r="F3" s="2">
+        <v>16819614.956469975</v>
+      </c>
+      <c r="G3" s="2">
+        <v>17821519.770741165</v>
+      </c>
+      <c r="H3" s="2">
+        <v>21820209.720085628</v>
+      </c>
+      <c r="I3" s="2">
+        <v>22693018.108889055</v>
+      </c>
+      <c r="J3" s="2">
+        <v>23911972.695901938</v>
+      </c>
+      <c r="K3" s="2">
+        <v>28357519.930870902</v>
+      </c>
+      <c r="L3" s="2">
+        <v>29491820.728105735</v>
+      </c>
+      <c r="M3" s="2">
+        <v>35530084.303933442</v>
+      </c>
+      <c r="N3" s="2">
+        <v>38653374.832799129</v>
+      </c>
+      <c r="O3" s="2">
+        <v>41429605.318097256</v>
+      </c>
+      <c r="P3" s="2">
+        <v>41429605.318097256</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>41429605.318097256</v>
+      </c>
+      <c r="R3" s="2">
+        <v>43859025.623070143</v>
+      </c>
+      <c r="S3" s="2">
+        <v>43859025.623070143</v>
+      </c>
+      <c r="T3" s="2">
+        <v>46565294.400521696</v>
+      </c>
+      <c r="U3" s="2">
+        <v>46565294.400521696</v>
+      </c>
+      <c r="V3" s="2">
+        <v>49063926.82361424</v>
+      </c>
+      <c r="W3" s="2">
+        <v>49063926.82361424</v>
+      </c>
+      <c r="X3" s="2">
+        <v>51215249.339896925</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>51215249.339896925</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>51215249.339896925</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>51215249.339896925</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>51215249.339896925</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -723,82 +750,82 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -809,82 +836,82 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>70</v>
+        <v>517553.69402880006</v>
       </c>
       <c r="I5">
-        <v>72</v>
+        <v>412167.35183295468</v>
       </c>
       <c r="J5">
-        <v>74</v>
+        <v>560146.92785662669</v>
       </c>
       <c r="K5">
-        <v>76</v>
+        <v>916125.71129999997</v>
       </c>
       <c r="L5">
-        <v>78</v>
+        <v>910610.96129999997</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>1365296.6420999998</v>
       </c>
       <c r="N5">
-        <v>82</v>
+        <v>1642420.9049999998</v>
       </c>
       <c r="O5">
-        <v>84</v>
+        <v>1784041.2501999999</v>
       </c>
       <c r="P5">
-        <v>86</v>
+        <v>1706935.2497999999</v>
       </c>
       <c r="Q5">
-        <v>88</v>
+        <v>1633362.2497999999</v>
       </c>
       <c r="R5">
-        <v>90</v>
+        <v>1751999.0734999997</v>
       </c>
       <c r="S5">
-        <v>92</v>
+        <v>1696500</v>
       </c>
       <c r="T5">
-        <v>94</v>
+        <v>1819062.80556</v>
       </c>
       <c r="U5">
-        <v>96</v>
+        <v>1741739.9999999998</v>
       </c>
       <c r="V5">
-        <v>98</v>
+        <v>1832800.1159999997</v>
       </c>
       <c r="W5">
-        <v>100</v>
+        <v>1755370.1159999995</v>
       </c>
       <c r="X5">
-        <v>102</v>
+        <v>1811730.1749899995</v>
       </c>
       <c r="Y5">
-        <v>104</v>
+        <v>1735173.6749999998</v>
       </c>
       <c r="Z5">
-        <v>106</v>
+        <v>1662054.5249999999</v>
       </c>
       <c r="AA5">
-        <v>108</v>
+        <v>1592060.0000100001</v>
       </c>
       <c r="AB5">
-        <v>110</v>
+        <v>1525190.4750000001</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -895,82 +922,82 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>45</v>
+        <v>557365.51664640009</v>
       </c>
       <c r="I6">
-        <v>46</v>
+        <v>522398.15523014031</v>
       </c>
       <c r="J6">
-        <v>47</v>
+        <v>709953.66437642218</v>
       </c>
       <c r="K6">
-        <v>48</v>
+        <v>1161136.07595</v>
       </c>
       <c r="L6">
-        <v>49</v>
+        <v>1154146.45095</v>
       </c>
       <c r="M6">
-        <v>50</v>
+        <v>1730434.1161500001</v>
       </c>
       <c r="N6">
-        <v>51</v>
+        <v>2081673.0075000001</v>
       </c>
       <c r="O6">
-        <v>52</v>
+        <v>2261168.5613000002</v>
       </c>
       <c r="P6">
-        <v>53</v>
+        <v>2163441.1886999998</v>
       </c>
       <c r="Q6">
-        <v>54</v>
+        <v>2070191.6887000001</v>
       </c>
       <c r="R6">
-        <v>55</v>
+        <v>2220556.9652499999</v>
       </c>
       <c r="S6">
-        <v>56</v>
+        <v>1930500</v>
       </c>
       <c r="T6">
-        <v>57</v>
+        <v>2069968.0201200002</v>
       </c>
       <c r="U6">
-        <v>58</v>
+        <v>1981980</v>
       </c>
       <c r="V6">
-        <v>59</v>
+        <v>2085600.132</v>
       </c>
       <c r="W6">
-        <v>60</v>
+        <v>1997490.1319999998</v>
       </c>
       <c r="X6">
-        <v>61</v>
+        <v>2061623.9922299997</v>
       </c>
       <c r="Y6">
-        <v>62</v>
+        <v>1974507.9750000001</v>
       </c>
       <c r="Z6">
-        <v>63</v>
+        <v>1891303.425</v>
       </c>
       <c r="AA6">
-        <v>64</v>
+        <v>1811654.4827699999</v>
       </c>
       <c r="AB6">
-        <v>65</v>
+        <v>1735561.575</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
@@ -981,82 +1008,776 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>70</v>
+        <v>2209556.1552768</v>
       </c>
       <c r="I7">
-        <v>74</v>
+        <v>2199823.4243177469</v>
       </c>
       <c r="J7">
-        <v>78</v>
+        <v>2989621.3940254841</v>
       </c>
       <c r="K7">
-        <v>82</v>
+        <v>4889554.6684499998</v>
       </c>
       <c r="L7">
-        <v>86</v>
+        <v>4860121.2934499998</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>7286873.9386500008</v>
       </c>
       <c r="N7">
-        <v>94</v>
+        <v>8765944.1325000003</v>
       </c>
       <c r="O7">
-        <v>98</v>
+        <v>9521801.5563000012</v>
       </c>
       <c r="P7">
-        <v>102</v>
+        <v>9110270.6937000006</v>
       </c>
       <c r="Q7">
-        <v>106</v>
+        <v>8717596.1937000006</v>
       </c>
       <c r="R7">
-        <v>110</v>
+        <v>9350785.75275</v>
       </c>
       <c r="S7">
-        <v>114</v>
+        <v>8482500</v>
       </c>
       <c r="T7">
-        <v>118</v>
+        <v>9095314.0277999993</v>
       </c>
       <c r="U7">
-        <v>122</v>
+        <v>8708700</v>
       </c>
       <c r="V7">
-        <v>126</v>
+        <v>9164000.5800000001</v>
       </c>
       <c r="W7">
-        <v>130</v>
+        <v>8776850.5799999982</v>
       </c>
       <c r="X7">
-        <v>134</v>
+        <v>9058650.8749499992</v>
       </c>
       <c r="Y7">
-        <v>138</v>
+        <v>8675868.375</v>
       </c>
       <c r="Z7">
-        <v>142</v>
+        <v>8310272.625</v>
       </c>
       <c r="AA7">
-        <v>146</v>
+        <v>7960300.0000499999</v>
       </c>
       <c r="AB7">
-        <v>150</v>
+        <v>7625952.375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BACB8C9-B9B0-3742-97F6-4323486816FC}">
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="D2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="E2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="F2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="G2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="H2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="I2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="J2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="K2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="L2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="M2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="N2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="O2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="P2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="Q2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="R2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="S2">
+        <v>0.379</v>
+      </c>
+      <c r="T2">
+        <v>0.379</v>
+      </c>
+      <c r="U2">
+        <v>0.379</v>
+      </c>
+      <c r="V2">
+        <v>0.379</v>
+      </c>
+      <c r="W2">
+        <v>0.379</v>
+      </c>
+      <c r="X2">
+        <v>0.379</v>
+      </c>
+      <c r="Y2">
+        <v>0.379</v>
+      </c>
+      <c r="Z2">
+        <v>0.379</v>
+      </c>
+      <c r="AA2">
+        <v>0.379</v>
+      </c>
+      <c r="AB2">
+        <v>0.379</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0.104</v>
+      </c>
+      <c r="D3">
+        <v>0.104</v>
+      </c>
+      <c r="E3">
+        <v>0.104</v>
+      </c>
+      <c r="F3">
+        <v>0.104</v>
+      </c>
+      <c r="G3">
+        <v>0.104</v>
+      </c>
+      <c r="H3">
+        <v>0.104</v>
+      </c>
+      <c r="I3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="J3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="K3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="L3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="M3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="N3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="O3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="P3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="Q3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="R3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="S3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="T3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="U3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="V3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="W3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="X3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="Y3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="Z3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="AA3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="AB3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0.112</v>
+      </c>
+      <c r="D4">
+        <v>0.112</v>
+      </c>
+      <c r="E4">
+        <v>0.112</v>
+      </c>
+      <c r="F4">
+        <v>0.112</v>
+      </c>
+      <c r="G4">
+        <v>0.112</v>
+      </c>
+      <c r="H4">
+        <v>0.112</v>
+      </c>
+      <c r="I4">
+        <v>0.109</v>
+      </c>
+      <c r="J4">
+        <v>0.109</v>
+      </c>
+      <c r="K4">
+        <v>0.109</v>
+      </c>
+      <c r="L4">
+        <v>0.109</v>
+      </c>
+      <c r="M4">
+        <v>0.109</v>
+      </c>
+      <c r="N4">
+        <v>0.109</v>
+      </c>
+      <c r="O4">
+        <v>0.109</v>
+      </c>
+      <c r="P4">
+        <v>0.109</v>
+      </c>
+      <c r="Q4">
+        <v>0.109</v>
+      </c>
+      <c r="R4">
+        <v>0.109</v>
+      </c>
+      <c r="S4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="T4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="U4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="V4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="W4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="X4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="Y4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="Z4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="AA4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="AB4">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="D5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="F5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="H5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="J5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="K5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="L5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="M5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="N5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="O5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="P5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="Q5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="R5">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="S5">
+        <v>0.435</v>
+      </c>
+      <c r="T5">
+        <v>0.435</v>
+      </c>
+      <c r="U5">
+        <v>0.435</v>
+      </c>
+      <c r="V5">
+        <v>0.435</v>
+      </c>
+      <c r="W5">
+        <v>0.435</v>
+      </c>
+      <c r="X5">
+        <v>0.435</v>
+      </c>
+      <c r="Y5">
+        <v>0.435</v>
+      </c>
+      <c r="Z5">
+        <v>0.435</v>
+      </c>
+      <c r="AA5">
+        <v>0.435</v>
+      </c>
+      <c r="AB5">
+        <v>0.435</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>4976477827.2000008</v>
+      </c>
+      <c r="I6">
+        <v>4792643625.9645901</v>
+      </c>
+      <c r="J6">
+        <v>6513336370.4258909</v>
+      </c>
+      <c r="K6">
+        <v>10652624550</v>
+      </c>
+      <c r="L6">
+        <v>10588499550</v>
+      </c>
+      <c r="M6">
+        <v>15875542350</v>
+      </c>
+      <c r="N6">
+        <v>19097917500</v>
+      </c>
+      <c r="O6">
+        <v>20744665700</v>
+      </c>
+      <c r="P6">
+        <v>19848084300</v>
+      </c>
+      <c r="Q6">
+        <v>18992584300</v>
+      </c>
+      <c r="R6">
+        <v>20372082250</v>
+      </c>
+      <c r="S6">
+        <v>19500000000</v>
+      </c>
+      <c r="T6">
+        <v>20908767880</v>
+      </c>
+      <c r="U6">
+        <v>20020000000</v>
+      </c>
+      <c r="V6">
+        <v>21066668000</v>
+      </c>
+      <c r="W6">
+        <v>20176667999.999996</v>
+      </c>
+      <c r="X6">
+        <v>20824484769.999996</v>
+      </c>
+      <c r="Y6">
+        <v>19944525000</v>
+      </c>
+      <c r="Z6">
+        <v>19104075000</v>
+      </c>
+      <c r="AA6">
+        <v>18299540230</v>
+      </c>
+      <c r="AB6">
+        <v>17530925000</v>
       </c>
     </row>
   </sheetData>

--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90EDCEDF-9F7E-694E-8ED3-E824D6A77DDF}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EB854DB-FA5B-444A-BC35-5A2E387C0A39}"/>
   <bookViews>
-    <workbookView xWindow="-9700" yWindow="760" windowWidth="25720" windowHeight="16980" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>

--- a/data/scenarios.xlsx
+++ b/data/scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EB854DB-FA5B-444A-BC35-5A2E387C0A39}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{84D30074-6CA2-9646-BF7A-0F0212785F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{696157B1-82BA-3840-8612-8253AFBD28AE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" xr2:uid="{8A7290D0-0CEE-BE47-A4B5-AA6B65E25749}"/>
   </bookViews>
@@ -664,82 +664,82 @@
         <v>9</v>
       </c>
       <c r="C3" s="2">
-        <v>13545909.750548668</v>
+        <v>966657.03881434398</v>
       </c>
       <c r="D3" s="2">
-        <v>14819212.824570615</v>
+        <v>2467521.2518916139</v>
       </c>
       <c r="E3" s="2">
-        <v>16172706.688913438</v>
+        <v>4086906.9687214158</v>
       </c>
       <c r="F3" s="2">
-        <v>16819614.956469975</v>
+        <v>4250383.2474702718</v>
       </c>
       <c r="G3" s="2">
-        <v>17821519.770741165</v>
+        <v>5078308.5278538484</v>
       </c>
       <c r="H3" s="2">
-        <v>21820209.720085628</v>
+        <v>11234183.3223552</v>
       </c>
       <c r="I3" s="2">
-        <v>22693018.108889055</v>
+        <v>11683550.655249387</v>
       </c>
       <c r="J3" s="2">
-        <v>23911972.695901938</v>
+        <v>12462126.544116681</v>
       </c>
       <c r="K3" s="2">
-        <v>28357519.930870902</v>
+        <v>18488000.976255953</v>
       </c>
       <c r="L3" s="2">
-        <v>29491820.728105735</v>
+        <v>19227521.01530619</v>
       </c>
       <c r="M3" s="2">
-        <v>35530084.303933442</v>
+        <v>26406961.963692084</v>
       </c>
       <c r="N3" s="2">
-        <v>38653374.832799129</v>
+        <v>31362092.688787885</v>
       </c>
       <c r="O3" s="2">
-        <v>41429605.318097256</v>
+        <v>35739728.489622861</v>
       </c>
       <c r="P3" s="2">
-        <v>41429605.318097256</v>
+        <v>35739728.489622861</v>
       </c>
       <c r="Q3" s="2">
-        <v>41429605.318097256</v>
+        <v>35739728.489622861</v>
       </c>
       <c r="R3" s="2">
-        <v>43859025.623070143</v>
+        <v>39575033.537424251</v>
       </c>
       <c r="S3" s="2">
-        <v>43859025.623070143</v>
+        <v>39575033.537424251</v>
       </c>
       <c r="T3" s="2">
-        <v>46565294.400521696</v>
+        <v>43833051.675945982</v>
       </c>
       <c r="U3" s="2">
-        <v>46565294.400521696</v>
+        <v>43833051.675945982</v>
       </c>
       <c r="V3" s="2">
-        <v>49063926.82361424</v>
+        <v>47807397.905829579</v>
       </c>
       <c r="W3" s="2">
-        <v>49063926.82361424</v>
+        <v>47807397.905829579</v>
       </c>
       <c r="X3" s="2">
-        <v>51215249.339896925</v>
+        <v>51215249.339896932</v>
       </c>
       <c r="Y3" s="2">
-        <v>51215249.339896925</v>
+        <v>51215249.339896932</v>
       </c>
       <c r="Z3" s="2">
-        <v>51215249.339896925</v>
+        <v>51215249.339896932</v>
       </c>
       <c r="AA3" s="2">
-        <v>51215249.339896925</v>
+        <v>51215249.339896932</v>
       </c>
       <c r="AB3" s="2">
-        <v>51215249.339896925</v>
+        <v>51215249.339896932</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -836,82 +836,108 @@
         <v>5</v>
       </c>
       <c r="C5">
+        <f>h2portion!C6*h2portion!C3</f>
         <v>0</v>
       </c>
       <c r="D5">
+        <f>h2portion!D6*h2portion!D3</f>
         <v>0</v>
       </c>
       <c r="E5">
+        <f>h2portion!E6*h2portion!E3</f>
         <v>0</v>
       </c>
       <c r="F5">
+        <f>h2portion!F6*h2portion!F3</f>
         <v>0</v>
       </c>
       <c r="G5">
+        <f>h2portion!G6*h2portion!G3</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <v>517553.6940288</v>
+        <f>h2portion!H6*h2portion!H3</f>
+        <v>517553.69402880006</v>
       </c>
       <c r="I5">
-        <v>412167.35183295468</v>
+        <f>h2portion!I6*h2portion!I3</f>
+        <v>412167.35183295474</v>
       </c>
       <c r="J5">
-        <v>560146.92785662669</v>
+        <f>h2portion!J6*h2portion!J3</f>
+        <v>560146.92785662657</v>
       </c>
       <c r="K5">
+        <f>h2portion!K6*h2portion!K3</f>
         <v>916125.71129999997</v>
       </c>
       <c r="L5">
+        <f>h2portion!L6*h2portion!L3</f>
         <v>910610.96129999997</v>
       </c>
       <c r="M5">
+        <f>h2portion!M6*h2portion!M3</f>
         <v>1365296.6420999998</v>
       </c>
       <c r="N5">
+        <f>h2portion!N6*h2portion!N3</f>
         <v>1642420.9049999998</v>
       </c>
       <c r="O5">
+        <f>h2portion!O6*h2portion!O3</f>
         <v>1784041.2501999999</v>
       </c>
       <c r="P5">
+        <f>h2portion!P6*h2portion!P3</f>
         <v>1706935.2497999999</v>
       </c>
       <c r="Q5">
+        <f>h2portion!Q6*h2portion!Q3</f>
         <v>1633362.2497999999</v>
       </c>
       <c r="R5">
-        <v>1751999.0734999997</v>
+        <f>h2portion!R6*h2portion!R3</f>
+        <v>1751999.0734999999</v>
       </c>
       <c r="S5">
-        <v>1696500</v>
+        <f>h2portion!S6*h2portion!S3</f>
+        <v>1696499.9999999998</v>
       </c>
       <c r="T5">
-        <v>1819062.80556</v>
+        <f>h2portion!T6*h2portion!T3</f>
+        <v>1819062.8055599998</v>
       </c>
       <c r="U5">
+        <f>h2portion!U6*h2portion!U3</f>
         <v>1741739.9999999998</v>
       </c>
       <c r="V5">
-        <v>1832800.1159999997</v>
+        <f>h2portion!V6*h2portion!V3</f>
+        <v>1832800.1159999999</v>
       </c>
       <c r="W5">
+        <f>h2portion!W6*h2portion!W3</f>
         <v>1755370.1159999995</v>
       </c>
       <c r="X5">
+        <f>h2portion!X6*h2portion!X3</f>
         <v>1811730.1749899995</v>
       </c>
       <c r="Y5">
+        <f>h2portion!Y6*h2portion!Y3</f>
         <v>1735173.6749999998</v>
       </c>
       <c r="Z5">
+        <f>h2portion!Z6*h2portion!Z3</f>
         <v>1662054.5249999999</v>
       </c>
       <c r="AA5">
-        <v>1592060.0000100001</v>
+        <f>h2portion!AA6*h2portion!AA3</f>
+        <v>1592060.0000099998</v>
       </c>
       <c r="AB5">
-        <v>1525190.4750000001</v>
+        <f>h2portion!AB6*h2portion!AB3</f>
+        <v>1525190.4749999999</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -922,82 +948,108 @@
         <v>6</v>
       </c>
       <c r="C6">
+        <f>h2portion!C6*h2portion!C4</f>
         <v>0</v>
       </c>
       <c r="D6">
+        <f>h2portion!D6*h2portion!D4</f>
         <v>0</v>
       </c>
       <c r="E6">
+        <f>h2portion!E6*h2portion!E4</f>
         <v>0</v>
       </c>
       <c r="F6">
+        <f>h2portion!F6*h2portion!F4</f>
         <v>0</v>
       </c>
       <c r="G6">
+        <f>h2portion!G6*h2portion!G4</f>
         <v>0</v>
       </c>
       <c r="H6">
+        <f>h2portion!H6*h2portion!H4</f>
         <v>557365.51664640009</v>
       </c>
       <c r="I6">
-        <v>522398.15523014031</v>
+        <f>h2portion!I6*h2portion!I4</f>
+        <v>522398.15523014037</v>
       </c>
       <c r="J6">
+        <f>h2portion!J6*h2portion!J4</f>
         <v>709953.66437642218</v>
       </c>
       <c r="K6">
+        <f>h2portion!K6*h2portion!K4</f>
         <v>1161136.07595</v>
       </c>
       <c r="L6">
+        <f>h2portion!L6*h2portion!L4</f>
         <v>1154146.45095</v>
       </c>
       <c r="M6">
-        <v>1730434.1161500001</v>
+        <f>h2portion!M6*h2portion!M4</f>
+        <v>1730434.1161499999</v>
       </c>
       <c r="N6">
+        <f>h2portion!N6*h2portion!N4</f>
         <v>2081673.0075000001</v>
       </c>
       <c r="O6">
-        <v>2261168.5613000002</v>
+        <f>h2portion!O6*h2portion!O4</f>
+        <v>2261168.5612999997</v>
       </c>
       <c r="P6">
-        <v>2163441.1886999998</v>
+        <f>h2portion!P6*h2portion!P4</f>
+        <v>2163441.1887000003</v>
       </c>
       <c r="Q6">
+        <f>h2portion!Q6*h2portion!Q4</f>
         <v>2070191.6887000001</v>
       </c>
       <c r="R6">
+        <f>h2portion!R6*h2portion!R4</f>
         <v>2220556.9652499999</v>
       </c>
       <c r="S6">
+        <f>h2portion!S6*h2portion!S4</f>
         <v>1930500</v>
       </c>
       <c r="T6">
-        <v>2069968.0201200002</v>
+        <f>h2portion!T6*h2portion!T4</f>
+        <v>2069968.02012</v>
       </c>
       <c r="U6">
+        <f>h2portion!U6*h2portion!U4</f>
         <v>1981980</v>
       </c>
       <c r="V6">
+        <f>h2portion!V6*h2portion!V4</f>
         <v>2085600.132</v>
       </c>
       <c r="W6">
+        <f>h2portion!W6*h2portion!W4</f>
         <v>1997490.1319999998</v>
       </c>
       <c r="X6">
+        <f>h2portion!X6*h2portion!X4</f>
         <v>2061623.9922299997</v>
       </c>
       <c r="Y6">
+        <f>h2portion!Y6*h2portion!Y4</f>
         <v>1974507.9750000001</v>
       </c>
       <c r="Z6">
+        <f>h2portion!Z6*h2portion!Z4</f>
         <v>1891303.425</v>
       </c>
       <c r="AA6">
-        <v>1811654.4827699999</v>
+        <f>h2portion!AA6*h2portion!AA4</f>
+        <v>1811654.4827700001</v>
       </c>
       <c r="AB6">
-        <v>1735561.575</v>
+        <f>h2portion!AB6*h2portion!AB4</f>
+        <v>1735561.5750000002</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
@@ -1023,67 +1075,67 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>2209556.1552768</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>2199823.4243177469</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>2989621.3940254841</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>4889554.6684499998</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>4860121.2934499998</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>7286873.9386500008</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>8765944.1325000003</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>9521801.5563000012</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>9110270.6937000006</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>8717596.1937000006</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>9350785.75275</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>8482500</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>9095314.0277999993</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>8708700</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>9164000.5800000001</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>8776850.5799999982</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>9058650.8749499992</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>8675868.375</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>8310272.625</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>7960300.0000499999</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>7625952.375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -1720,67 +1772,67 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4976477827.1999998</v>
+        <v>4976477.8272000011</v>
       </c>
       <c r="I6">
-        <v>4792643625.9645901</v>
+        <v>4792643.6259645903</v>
       </c>
       <c r="J6">
-        <v>6513336370.4258909</v>
+        <v>6513336.3704258911</v>
       </c>
       <c r="K6">
-        <v>10652624550</v>
+        <v>10652624.550000001</v>
       </c>
       <c r="L6">
-        <v>10588499550</v>
+        <v>10588499.550000001</v>
       </c>
       <c r="M6">
-        <v>15875542350</v>
+        <v>15875542.35</v>
       </c>
       <c r="N6">
-        <v>19097917500</v>
+        <v>19097917.5</v>
       </c>
       <c r="O6">
-        <v>20744665700</v>
+        <v>20744665.699999999</v>
       </c>
       <c r="P6">
-        <v>19848084300</v>
+        <v>19848084.300000001</v>
       </c>
       <c r="Q6">
-        <v>18992584300</v>
+        <v>18992584.300000001</v>
       </c>
       <c r="R6">
-        <v>20372082250</v>
+        <v>20372082.25</v>
       </c>
       <c r="S6">
-        <v>19500000000</v>
+        <v>19500000</v>
       </c>
       <c r="T6">
-        <v>20908767880</v>
+        <v>20908767.879999999</v>
       </c>
       <c r="U6">
-        <v>20020000000</v>
+        <v>20020000</v>
       </c>
       <c r="V6">
-        <v>21066668000</v>
+        <v>21066668</v>
       </c>
       <c r="W6">
-        <v>20176667999.999996</v>
+        <v>20176667.999999996</v>
       </c>
       <c r="X6">
-        <v>20824484769.999996</v>
+        <v>20824484.769999996</v>
       </c>
       <c r="Y6">
-        <v>19944525000</v>
+        <v>19944525</v>
       </c>
       <c r="Z6">
-        <v>19104075000</v>
+        <v>19104075</v>
       </c>
       <c r="AA6">
-        <v>18299540230</v>
+        <v>18299540.23</v>
       </c>
       <c r="AB6">
-        <v>17530925000</v>
+        <v>17530925</v>
       </c>
     </row>
   </sheetData>
